--- a/category/category_template.xlsx
+++ b/category/category_template.xlsx
@@ -1,45 +1,44 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
-  <workbookPr/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\miche\OneDrive\Desktop\Agentic-SEO\category\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D60C9B5-FAF7-4651-AF33-E37BF1A63A84}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{5D94E12E-2A27-4766-93A7-A9B13BAD66BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="732" yWindow="744" windowWidth="18444" windowHeight="10488" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-96" yWindow="0" windowWidth="11712" windowHeight="12336" xr2:uid="{0ECB34CB-D1A2-40FA-8959-C7B1E2241AC4}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Foglio1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="5">
   <si>
     <t>Brand</t>
-  </si>
-  <si>
-    <t>Descrizione</t>
-  </si>
-  <si>
-    <t>INPUT</t>
-  </si>
-  <si>
-    <t>Categoria-HTML</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> </t>
   </si>
   <si>
     <t>Categoria_1</t>
@@ -51,7 +50,7 @@
     <t>Categoria_3</t>
   </si>
   <si>
-    <t>Alt_Categoria-HTML</t>
+    <t>Descrizione</t>
   </si>
 </sst>
 </file>
@@ -62,107 +61,23 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF92D050"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="7">
+  <borders count="1">
     <border>
       <left/>
       <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
       <top/>
       <bottom/>
       <diagonal/>
@@ -171,15 +86,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normale" xfId="0" builtinId="0"/>
@@ -198,7 +106,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema di Office">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -208,39 +116,39 @@
         <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="44546A"/>
+        <a:srgbClr val="0E2841"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="E7E6E6"/>
+        <a:srgbClr val="E8E8E8"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="5B9BD5"/>
+        <a:srgbClr val="156082"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="ED7D31"/>
+        <a:srgbClr val="E97132"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="A5A5A5"/>
+        <a:srgbClr val="196B24"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="FFC000"/>
+        <a:srgbClr val="0F9ED5"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="4472C4"/>
+        <a:srgbClr val="A02B93"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="70AD47"/>
+        <a:srgbClr val="4EA72E"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0563C1"/>
+        <a:srgbClr val="467886"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="954F72"/>
+        <a:srgbClr val="96607D"/>
       </a:folHlink>
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
+        <a:latin typeface="Aptos Display" panose="02110004020202020204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック Light"/>
@@ -273,9 +181,26 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Aptos Narrow" panose="02110004020202020204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック"/>
@@ -308,6 +233,23 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -369,13 +311,6 @@
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
-        </a:ln>
         <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
@@ -384,6 +319,13 @@
           <a:miter lim="800000"/>
         </a:ln>
         <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
@@ -448,65 +390,55 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults/>
+  <a:objectDefaults>
+    <a:lnDef>
+      <a:spPr/>
+      <a:bodyPr/>
+      <a:lstStyle/>
+      <a:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </a:style>
+    </a:lnDef>
+  </a:objectDefaults>
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G11"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A94FE66C-08B9-4977-A4D7-BEDE8A78688F}">
+  <dimension ref="A1:E1"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="14.33203125" customWidth="1"/>
-    <col min="2" max="2" width="13.88671875" customWidth="1"/>
-    <col min="3" max="3" width="15.21875" customWidth="1"/>
-    <col min="4" max="4" width="10.109375" customWidth="1"/>
-    <col min="5" max="5" width="17.77734375" customWidth="1"/>
-    <col min="6" max="7" width="23" customWidth="1"/>
-  </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1" t="s">
         <v>2</v>
       </c>
-      <c r="B1" s="2"/>
-      <c r="C1" s="2"/>
-      <c r="D1" s="2"/>
-      <c r="E1" s="2"/>
-      <c r="F1" s="4"/>
-      <c r="G1" s="6"/>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A2" s="5" t="s">
-        <v>5</v>
+      <c r="C1" t="s">
+        <v>3</v>
       </c>
-      <c r="B2" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C2" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="D2" s="5" t="s">
+      <c r="D1" t="s">
         <v>0</v>
       </c>
-      <c r="E2" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="F2" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G2" s="7" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="E11" t="s">
+      <c r="E1" t="s">
         <v>4</v>
       </c>
     </row>

--- a/category/category_template.xlsx
+++ b/category/category_template.xlsx
@@ -1,49 +1,153 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Foglio1" sheetId="1" r:id="Rbf10e12803e14ed4"/>
-  </x:sheets>
-</x:workbook>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <workbookPr defaultThemeVersion="202300"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\LAVORO\BRICOFER\SITO\AI\AI CONTENUTI SEO\nuove richieste\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B76E26C-B7D3-496B-8250-6FD0C1DE46F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <bookViews>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{0ECB34CB-D1A2-40FA-8959-C7B1E2241AC4}"/>
+  </bookViews>
+  <sheets>
+    <sheet name="Foglio1" sheetId="1" r:id="rId1"/>
+  </sheets>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+      <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
+</workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
+  <si>
+    <t>Brand</t>
+  </si>
+  <si>
+    <t>Categoria_1</t>
+  </si>
+  <si>
+    <t>Categoria_2</t>
+  </si>
+  <si>
+    <t>Categoria_3</t>
+  </si>
+  <si>
+    <t>Descrizione</t>
+  </si>
+  <si>
+    <t>Scheda_Tecnica</t>
+  </si>
+  <si>
+    <t>Informazioni</t>
+  </si>
+  <si>
+    <t>Prodotti Tecnici e Chimici</t>
+  </si>
+  <si>
+    <t>Beta</t>
+  </si>
+  <si>
+    <t>Detergenti Tecnici</t>
+  </si>
+  <si>
+    <t>Detergenti Sgrassanti</t>
+  </si>
+  <si>
+    <t>https://www.beta-tools.com/it/</t>
+  </si>
+  <si>
+    <t>https://faren.com/</t>
+  </si>
+  <si>
+    <t>https://faren.com/en/category/retail/detergents-en-r/</t>
+  </si>
+</sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:fonts count="1">
-    <x:font>
-      <x:sz val="11"/>
-      <x:color theme="1"/>
-      <x:name val="Aptos Narrow"/>
-    </x:font>
-  </x:fonts>
-  <x:fills count="2">
-    <x:fill>
-      <x:patternFill patternType="none"/>
-    </x:fill>
-    <x:fill>
-      <x:patternFill patternType="gray125"/>
-    </x:fill>
-  </x:fills>
-  <x:borders count="1">
-    <x:border/>
-  </x:borders>
-  <x:cellStyleXfs count="1">
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-  </x:cellStyleXfs>
-  <x:cellXfs count="2">
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment wrapText="0"/>
-    </x:xf>
-  </x:cellXfs>
-  <x:cellStyles count="1">
-    <x:cellStyle name="Normale" xfId="0"/>
-  </x:cellStyles>
-</x:styleSheet>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="1" x14ac:knownFonts="1">
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+  </fonts>
+  <fills count="2">
+    <fill>
+      <patternFill patternType="none"/>
+    </fill>
+    <fill>
+      <patternFill patternType="gray125"/>
+    </fill>
+  </fills>
+  <borders count="2">
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFD9E2F3"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFD9E2F3"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFD9E2F3"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFD9E2F3"/>
+      </bottom>
+      <diagonal/>
+    </border>
+  </borders>
+  <cellStyleXfs count="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+  </cellStyleXfs>
+  <cellXfs count="2">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+  </cellXfs>
+  <cellStyles count="1">
+    <cellStyle name="Normale" xfId="0" builtinId="0"/>
+  </cellStyles>
+  <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
+</styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -89,14 +193,108 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri Light"/>
-        <a:ea typeface="Calibri Light"/>
-        <a:cs typeface="Calibri Light"/>
+        <a:latin typeface="Aptos Display" panose="02110004020202020204"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="游ゴシック Light"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="等线 Light"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Times New Roman"/>
+        <a:font script="Hebr" typeface="Times New Roman"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="MoolBoran"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Times New Roman"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
-        <a:ea typeface="Calibri"/>
-        <a:cs typeface="Calibri"/>
+        <a:latin typeface="Aptos Narrow" panose="02110004020202020204"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="游ゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="等线"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Arial"/>
+        <a:font script="Hebr" typeface="Arial"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="DaunPenh"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Arial"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -108,23 +306,23 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="67000"/>
                 <a:lumMod val="110000"/>
                 <a:satMod val="105000"/>
+                <a:tint val="67000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="50000">
               <a:schemeClr val="phClr">
-                <a:tint val="73000"/>
                 <a:lumMod val="105000"/>
                 <a:satMod val="103000"/>
+                <a:tint val="73000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:tint val="81000"/>
                 <a:lumMod val="105000"/>
                 <a:satMod val="109000"/>
+                <a:tint val="81000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
@@ -134,23 +332,23 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
+                <a:satMod val="103000"/>
+                <a:lumMod val="102000"/>
                 <a:tint val="94000"/>
-                <a:lumMod val="102000"/>
-                <a:satMod val="103000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="50000">
               <a:schemeClr val="phClr">
+                <a:satMod val="110000"/>
+                <a:lumMod val="100000"/>
                 <a:shade val="100000"/>
-                <a:lumMod val="100000"/>
-                <a:satMod val="110000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:shade val="78000"/>
                 <a:lumMod val="99000"/>
                 <a:satMod val="120000"/>
+                <a:shade val="78000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
@@ -158,23 +356,26 @@
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="12700">
+        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
         </a:ln>
-        <a:ln w="19050">
+        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
         </a:ln>
-        <a:ln w="25400">
+        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
         </a:ln>
       </a:lnStyleLst>
       <a:effectStyleLst>
@@ -209,17 +410,17 @@
             <a:gs pos="0">
               <a:schemeClr val="phClr">
                 <a:tint val="93000"/>
+                <a:satMod val="150000"/>
                 <a:shade val="98000"/>
                 <a:lumMod val="102000"/>
-                <a:satMod val="150000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="50000">
               <a:schemeClr val="phClr">
                 <a:tint val="98000"/>
+                <a:satMod val="130000"/>
                 <a:shade val="90000"/>
                 <a:lumMod val="103000"/>
-                <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
@@ -234,46 +435,97 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults>
+    <a:lnDef>
+      <a:spPr/>
+      <a:bodyPr/>
+      <a:lstStyle/>
+      <a:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </a:style>
+    </a:lnDef>
+  </a:objectDefaults>
+  <a:extraClrSchemeLst/>
+  <a:extLst>
+    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
+    </a:ext>
+  </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:sheetFormatPr defaultRowHeight="14.399999618530273"/>
-  <x:cols>
-    <x:col min="1" max="1" width="24" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="24" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="24" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="14" hidden="0" customWidth="1"/>
-    <x:col min="5" max="5" width="28" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="28" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="28" hidden="0" customWidth="1"/>
-  </x:cols>
-  <x:sheetData>
-    <x:row r="1">
-      <x:c r="A1" s="1" t="str">
-        <x:v>Categoria_1</x:v>
-      </x:c>
-      <x:c r="B1" s="1" t="str">
-        <x:v>Categoria_2</x:v>
-      </x:c>
-      <x:c r="C1" s="1" t="str">
-        <x:v>Categoria_3</x:v>
-      </x:c>
-      <x:c r="D1" s="1" t="str">
-        <x:v>Brand</x:v>
-      </x:c>
-      <x:c r="E1" s="1" t="str">
-        <x:v>Descrizione</x:v>
-      </x:c>
-      <x:c r="F1" s="1" t="str">
-        <x:v>Scheda_Tecnica</x:v>
-      </x:c>
-      <x:c r="G1" s="1" t="str">
-        <x:v>Informazioni</x:v>
-      </x:c>
-    </x:row>
-  </x:sheetData>
-  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</x:worksheet>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A94FE66C-08B9-4977-A4D7-BEDE8A78688F}">
+  <dimension ref="A1:G2"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="23.7265625" customWidth="1"/>
+    <col min="2" max="2" width="17.1796875" customWidth="1"/>
+    <col min="3" max="3" width="20.7265625" customWidth="1"/>
+    <col min="4" max="4" width="10.7265625" customWidth="1"/>
+    <col min="5" max="5" width="30.90625" customWidth="1"/>
+    <col min="6" max="6" width="18.36328125" customWidth="1"/>
+    <col min="7" max="7" width="46.6328125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D1" t="s">
+        <v>0</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" ht="16" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>